--- a/log/matrix_data_simVreal.xlsx
+++ b/log/matrix_data_simVreal.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="12520"/>
+    <workbookView windowWidth="28260" windowHeight="12680"/>
   </bookViews>
   <sheets>
     <sheet name="matrix_data_simVreal" sheetId="1" r:id="rId1"/>
